--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T16:07:27+00:00</t>
+    <t>2026-08-31T20:29:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T20:29:59+00:00</t>
+    <t>2026-09-01T08:25:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:25:15+00:00</t>
+    <t>2026-09-01T09:40:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:40:46+00:00</t>
+    <t>2026-09-01T10:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T10:03:55+00:00</t>
+    <t>2026-09-01T13:17:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:17:32+00:00</t>
+    <t>2026-09-03T11:23:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T11:23:31+00:00</t>
+    <t>2026-09-03T16:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T16:19:13+00:00</t>
+    <t>2026-09-08T13:04:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
+++ b/StructureDefinition-mii-pr-sdd-datenerhebung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:04:20+00:00</t>
+    <t>2026-09-08T13:56:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
